--- a/estimates/output/jhr_se15/jhr_se15_estimates.xlsx
+++ b/estimates/output/jhr_se15/jhr_se15_estimates.xlsx
@@ -583,13 +583,13 @@
         <v>1367553</v>
       </c>
       <c r="E4" t="n">
-        <v>62.74</v>
+        <v>62.81</v>
       </c>
       <c r="F4" t="n">
-        <v>61.45</v>
+        <v>61.58</v>
       </c>
       <c r="G4" t="n">
-        <v>64.15000000000001</v>
+        <v>64.22</v>
       </c>
       <c r="H4" t="n">
         <v>37.7</v>
@@ -641,13 +641,13 @@
         <v>1367553</v>
       </c>
       <c r="E5" t="n">
-        <v>35.94</v>
+        <v>35.9</v>
       </c>
       <c r="F5" t="n">
         <v>33.84</v>
       </c>
       <c r="G5" t="n">
-        <v>38.38</v>
+        <v>38.43</v>
       </c>
       <c r="H5" t="n">
         <v>15.98</v>
@@ -699,13 +699,13 @@
         <v>1367553</v>
       </c>
       <c r="E6" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="F6" t="n">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="G6" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="H6" t="n">
         <v>0.27</v>
@@ -757,13 +757,13 @@
         <v>1367553</v>
       </c>
       <c r="E7" t="n">
-        <v>21.77</v>
+        <v>21.51</v>
       </c>
       <c r="F7" t="n">
-        <v>20.57</v>
+        <v>20.37</v>
       </c>
       <c r="G7" t="n">
-        <v>23.27</v>
+        <v>23.15</v>
       </c>
       <c r="H7" t="n">
         <v>7.4</v>
@@ -815,13 +815,13 @@
         <v>955008</v>
       </c>
       <c r="E8" t="n">
-        <v>44.54</v>
+        <v>44.49</v>
       </c>
       <c r="F8" t="n">
-        <v>42.87</v>
+        <v>43.03</v>
       </c>
       <c r="G8" t="n">
-        <v>46.22</v>
+        <v>46.06</v>
       </c>
       <c r="H8" t="n">
         <v>18.13</v>
@@ -873,13 +873,13 @@
         <v>955008</v>
       </c>
       <c r="E9" t="n">
-        <v>5.59</v>
+        <v>5.61</v>
       </c>
       <c r="F9" t="n">
-        <v>4.26</v>
+        <v>4.51</v>
       </c>
       <c r="G9" t="n">
-        <v>7.28</v>
+        <v>7.02</v>
       </c>
       <c r="H9" t="n">
         <v>0.51</v>
@@ -931,13 +931,13 @@
         <v>955008</v>
       </c>
       <c r="E10" t="n">
-        <v>31.7</v>
+        <v>31.45</v>
       </c>
       <c r="F10" t="n">
-        <v>27.13</v>
+        <v>27.16</v>
       </c>
       <c r="G10" t="n">
-        <v>35.37</v>
+        <v>35.01</v>
       </c>
       <c r="H10" t="n">
         <v>5.77</v>
@@ -989,13 +989,13 @@
         <v>955008</v>
       </c>
       <c r="E11" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="F11" t="n">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="H11" t="n">
         <v>0.01</v>
@@ -1047,13 +1047,13 @@
         <v>185594</v>
       </c>
       <c r="E12" t="n">
-        <v>34.02</v>
+        <v>33.07</v>
       </c>
       <c r="F12" t="n">
-        <v>24.29</v>
+        <v>24.83</v>
       </c>
       <c r="G12" t="n">
-        <v>43.06</v>
+        <v>41.18</v>
       </c>
       <c r="H12" t="n">
         <v>1.02</v>
@@ -1105,13 +1105,13 @@
         <v>185594</v>
       </c>
       <c r="E13" t="n">
-        <v>11.15</v>
+        <v>11.3</v>
       </c>
       <c r="F13" t="n">
-        <v>4.99</v>
+        <v>5.28</v>
       </c>
       <c r="G13" t="n">
-        <v>18.24</v>
+        <v>18.7</v>
       </c>
       <c r="H13" t="n">
         <v>0.15</v>
@@ -1163,13 +1163,13 @@
         <v>185594</v>
       </c>
       <c r="E14" t="n">
-        <v>12.07</v>
+        <v>13.27</v>
       </c>
       <c r="F14" t="n">
-        <v>4.04</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>19.06</v>
+        <v>17.91</v>
       </c>
       <c r="H14" t="n">
         <v>0.01</v>
@@ -1221,13 +1221,13 @@
         <v>185594</v>
       </c>
       <c r="E15" t="n">
-        <v>2.18</v>
+        <v>2.86</v>
       </c>
       <c r="F15" t="n">
-        <v>0.04</v>
+        <v>0.89</v>
       </c>
       <c r="G15" t="n">
-        <v>4.58</v>
+        <v>5.47</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1279,13 +1279,13 @@
         <v>66680</v>
       </c>
       <c r="E16" t="n">
-        <v>37.56</v>
+        <v>39.47</v>
       </c>
       <c r="F16" t="n">
-        <v>23.52</v>
+        <v>23.77</v>
       </c>
       <c r="G16" t="n">
-        <v>49.6</v>
+        <v>49.14</v>
       </c>
       <c r="H16" t="n">
         <v>2.31</v>
@@ -1337,13 +1337,13 @@
         <v>66680</v>
       </c>
       <c r="E17" t="n">
-        <v>15.35</v>
+        <v>15.38</v>
       </c>
       <c r="F17" t="n">
-        <v>2.26</v>
+        <v>4.26</v>
       </c>
       <c r="G17" t="n">
-        <v>25.49</v>
+        <v>24.17</v>
       </c>
       <c r="H17" t="n">
         <v>1.15</v>
@@ -1395,13 +1395,13 @@
         <v>66680</v>
       </c>
       <c r="E18" t="n">
-        <v>2.86</v>
+        <v>1.64</v>
       </c>
       <c r="F18" t="n">
-        <v>0.13</v>
+        <v>0.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.4</v>
+        <v>3.13</v>
       </c>
       <c r="H18" t="n">
         <v>0.11</v>
@@ -1453,13 +1453,13 @@
         <v>66680</v>
       </c>
       <c r="E19" t="n">
-        <v>15.15</v>
+        <v>17.1</v>
       </c>
       <c r="F19" t="n">
-        <v>7.45</v>
+        <v>11.93</v>
       </c>
       <c r="G19" t="n">
-        <v>20.98</v>
+        <v>21.01</v>
       </c>
       <c r="H19" t="n">
         <v>0.42</v>
@@ -1514,10 +1514,10 @@
         <v>51.45</v>
       </c>
       <c r="F20" t="n">
-        <v>49.58</v>
+        <v>49.65</v>
       </c>
       <c r="G20" t="n">
-        <v>53.31</v>
+        <v>53.29</v>
       </c>
       <c r="H20" t="n">
         <v>38.95</v>
@@ -1569,10 +1569,10 @@
         <v>677952</v>
       </c>
       <c r="E21" t="n">
-        <v>21.29</v>
+        <v>21.31</v>
       </c>
       <c r="F21" t="n">
-        <v>19.47</v>
+        <v>19.54</v>
       </c>
       <c r="G21" t="n">
         <v>23.38</v>
@@ -1627,13 +1627,13 @@
         <v>677952</v>
       </c>
       <c r="E22" t="n">
-        <v>11.52</v>
+        <v>11.56</v>
       </c>
       <c r="F22" t="n">
-        <v>9.49</v>
+        <v>9.6</v>
       </c>
       <c r="G22" t="n">
-        <v>13.48</v>
+        <v>13.45</v>
       </c>
       <c r="H22" t="n">
         <v>7.5</v>
@@ -1685,13 +1685,13 @@
         <v>677952</v>
       </c>
       <c r="E23" t="n">
-        <v>14.2</v>
+        <v>14.23</v>
       </c>
       <c r="F23" t="n">
-        <v>12.88</v>
+        <v>12.92</v>
       </c>
       <c r="G23" t="n">
-        <v>16.1</v>
+        <v>16.14</v>
       </c>
       <c r="H23" t="n">
         <v>8.23</v>
@@ -1743,10 +1743,10 @@
         <v>557295</v>
       </c>
       <c r="E24" t="n">
-        <v>46.54</v>
+        <v>46.5</v>
       </c>
       <c r="F24" t="n">
-        <v>45.12</v>
+        <v>45.13</v>
       </c>
       <c r="G24" t="n">
         <v>48.14</v>
@@ -1801,13 +1801,13 @@
         <v>557295</v>
       </c>
       <c r="E25" t="n">
-        <v>19.91</v>
+        <v>19.85</v>
       </c>
       <c r="F25" t="n">
-        <v>18.25</v>
+        <v>18.18</v>
       </c>
       <c r="G25" t="n">
-        <v>21.68</v>
+        <v>21.66</v>
       </c>
       <c r="H25" t="n">
         <v>5.95</v>
@@ -1859,13 +1859,13 @@
         <v>557295</v>
       </c>
       <c r="E26" t="n">
-        <v>9.710000000000001</v>
+        <v>9.69</v>
       </c>
       <c r="F26" t="n">
-        <v>8.220000000000001</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>11.24</v>
+        <v>11.25</v>
       </c>
       <c r="H26" t="n">
         <v>3.01</v>
@@ -1917,13 +1917,13 @@
         <v>557295</v>
       </c>
       <c r="E27" t="n">
-        <v>13.77</v>
+        <v>13.69</v>
       </c>
       <c r="F27" t="n">
-        <v>12.56</v>
+        <v>12.51</v>
       </c>
       <c r="G27" t="n">
-        <v>15.31</v>
+        <v>15.23</v>
       </c>
       <c r="H27" t="n">
         <v>3.6</v>
@@ -1975,13 +1975,13 @@
         <v>460337</v>
       </c>
       <c r="E28" t="n">
-        <v>52.02</v>
+        <v>52.08</v>
       </c>
       <c r="F28" t="n">
-        <v>49.77</v>
+        <v>49.82</v>
       </c>
       <c r="G28" t="n">
-        <v>54.25</v>
+        <v>54.27</v>
       </c>
       <c r="H28" t="n">
         <v>25.01</v>
@@ -2033,13 +2033,13 @@
         <v>460337</v>
       </c>
       <c r="E29" t="n">
-        <v>20.02</v>
+        <v>20.04</v>
       </c>
       <c r="F29" t="n">
-        <v>18.32</v>
+        <v>18.38</v>
       </c>
       <c r="G29" t="n">
-        <v>22.24</v>
+        <v>22.2</v>
       </c>
       <c r="H29" t="n">
         <v>4.61</v>
@@ -2094,10 +2094,10 @@
         <v>14.18</v>
       </c>
       <c r="F30" t="n">
-        <v>11.76</v>
+        <v>11.87</v>
       </c>
       <c r="G30" t="n">
-        <v>16.46</v>
+        <v>16.4</v>
       </c>
       <c r="H30" t="n">
         <v>3.85</v>
@@ -2149,7 +2149,7 @@
         <v>460337</v>
       </c>
       <c r="E31" t="n">
-        <v>13.47</v>
+        <v>13.52</v>
       </c>
       <c r="F31" t="n">
         <v>12.12</v>
@@ -2207,13 +2207,13 @@
         <v>384405</v>
       </c>
       <c r="E32" t="n">
-        <v>62.34</v>
+        <v>62.31</v>
       </c>
       <c r="F32" t="n">
-        <v>60.58</v>
+        <v>60.53</v>
       </c>
       <c r="G32" t="n">
-        <v>64.2</v>
+        <v>64.12</v>
       </c>
       <c r="H32" t="n">
         <v>30.65</v>
@@ -2265,13 +2265,13 @@
         <v>384405</v>
       </c>
       <c r="E33" t="n">
-        <v>24.68</v>
+        <v>24.69</v>
       </c>
       <c r="F33" t="n">
-        <v>22.77</v>
+        <v>22.79</v>
       </c>
       <c r="G33" t="n">
-        <v>26.89</v>
+        <v>27.01</v>
       </c>
       <c r="H33" t="n">
         <v>4.73</v>
@@ -2323,13 +2323,13 @@
         <v>384405</v>
       </c>
       <c r="E34" t="n">
-        <v>19.13</v>
+        <v>19.23</v>
       </c>
       <c r="F34" t="n">
-        <v>16.52</v>
+        <v>16.56</v>
       </c>
       <c r="G34" t="n">
-        <v>21.87</v>
+        <v>21.97</v>
       </c>
       <c r="H34" t="n">
         <v>5.19</v>
@@ -2381,13 +2381,13 @@
         <v>384405</v>
       </c>
       <c r="E35" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="F35" t="n">
-        <v>11.64</v>
+        <v>11.67</v>
       </c>
       <c r="G35" t="n">
-        <v>14.6</v>
+        <v>14.71</v>
       </c>
       <c r="H35" t="n">
         <v>1.58</v>
@@ -2439,13 +2439,13 @@
         <v>287427</v>
       </c>
       <c r="E36" t="n">
-        <v>65.34</v>
+        <v>65.23</v>
       </c>
       <c r="F36" t="n">
-        <v>63.87</v>
+        <v>63.88</v>
       </c>
       <c r="G36" t="n">
-        <v>67.14</v>
+        <v>66.92</v>
       </c>
       <c r="H36" t="n">
         <v>26.65</v>
@@ -2497,13 +2497,13 @@
         <v>287427</v>
       </c>
       <c r="E37" t="n">
-        <v>28.96</v>
+        <v>29.01</v>
       </c>
       <c r="F37" t="n">
-        <v>26.27</v>
+        <v>26.38</v>
       </c>
       <c r="G37" t="n">
-        <v>32.18</v>
+        <v>32.01</v>
       </c>
       <c r="H37" t="n">
         <v>5.05</v>
@@ -2555,13 +2555,13 @@
         <v>287427</v>
       </c>
       <c r="E38" t="n">
-        <v>21.35</v>
+        <v>21.26</v>
       </c>
       <c r="F38" t="n">
-        <v>18.25</v>
+        <v>18.13</v>
       </c>
       <c r="G38" t="n">
-        <v>24.42</v>
+        <v>24.31</v>
       </c>
       <c r="H38" t="n">
         <v>5.95</v>
@@ -2613,13 +2613,13 @@
         <v>287427</v>
       </c>
       <c r="E39" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="F39" t="n">
-        <v>8.57</v>
+        <v>8.56</v>
       </c>
       <c r="G39" t="n">
-        <v>11.1</v>
+        <v>11.16</v>
       </c>
       <c r="H39" t="n">
         <v>0.92</v>
@@ -2671,13 +2671,13 @@
         <v>207419</v>
       </c>
       <c r="E40" t="n">
-        <v>46.5</v>
+        <v>46.67</v>
       </c>
       <c r="F40" t="n">
-        <v>43.99</v>
+        <v>44.02</v>
       </c>
       <c r="G40" t="n">
-        <v>48.77</v>
+        <v>48.93</v>
       </c>
       <c r="H40" t="n">
         <v>19.91</v>
@@ -2729,13 +2729,13 @@
         <v>207419</v>
       </c>
       <c r="E41" t="n">
-        <v>24.18</v>
+        <v>24.19</v>
       </c>
       <c r="F41" t="n">
-        <v>21.29</v>
+        <v>21.3</v>
       </c>
       <c r="G41" t="n">
-        <v>27.09</v>
+        <v>27.16</v>
       </c>
       <c r="H41" t="n">
         <v>3.43</v>
@@ -2787,13 +2787,13 @@
         <v>207419</v>
       </c>
       <c r="E42" t="n">
-        <v>13.74</v>
+        <v>13.59</v>
       </c>
       <c r="F42" t="n">
-        <v>11.63</v>
+        <v>11.44</v>
       </c>
       <c r="G42" t="n">
-        <v>15.82</v>
+        <v>15.63</v>
       </c>
       <c r="H42" t="n">
         <v>3.54</v>
@@ -2845,13 +2845,13 @@
         <v>207419</v>
       </c>
       <c r="E43" t="n">
-        <v>4.71</v>
+        <v>4.65</v>
       </c>
       <c r="F43" t="n">
-        <v>4.01</v>
+        <v>4.03</v>
       </c>
       <c r="G43" t="n">
-        <v>5.48</v>
+        <v>5.38</v>
       </c>
       <c r="H43" t="n">
         <v>0.03</v>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -12526,7 +12526,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0.06</v>
@@ -12578,10 +12578,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E9" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -12633,7 +12633,7 @@
         <v>-0.04</v>
       </c>
       <c r="E11" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
@@ -12656,7 +12656,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="E12" t="n">
         <v>0.12</v>
@@ -12737,7 +12737,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -12760,10 +12760,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -12786,10 +12786,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -12812,10 +12812,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="E18" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -12838,10 +12838,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="E19" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.71</v>
+        <v>0.6</v>
       </c>
       <c r="E20" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -12890,10 +12890,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="E21" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
@@ -12916,10 +12916,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.52</v>
+        <v>0.41</v>
       </c>
       <c r="E22" t="n">
-        <v>3.08</v>
+        <v>2.94</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -12942,10 +12942,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="E23" t="n">
-        <v>4.52</v>
+        <v>4.41</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
@@ -12968,10 +12968,10 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="E24" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -12994,10 +12994,10 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.09</v>
+        <v>0.3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -13020,10 +13020,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
       <c r="E26" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -13046,10 +13046,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.72</v>
+        <v>1.01</v>
       </c>
       <c r="E27" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="F27" t="n">
         <v>1</v>
